--- a/E/SWAD2.xlsx
+++ b/E/SWAD2.xlsx
@@ -34,7 +34,7 @@
     <t>20008798</t>
   </si>
   <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
+    <t>S/Q CHUNKY CSHW 82 G</t>
   </si>
   <si>
     <t>2</t>
